--- a/tests/fixtures/plata-sample.xlsx
+++ b/tests/fixtures/plata-sample.xlsx
@@ -550,9 +550,6 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>1500</v>
-      </c>
       <c r="O2" t="n">
         <v>66796</v>
       </c>
@@ -601,9 +598,6 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>1295.45</v>
-      </c>
       <c r="O3" t="n">
         <v>75743.28</v>
       </c>
@@ -652,9 +646,6 @@
       <c r="J4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
-        <v>1261.36</v>
-      </c>
       <c r="O4" t="n">
         <v>77032.92</v>
       </c>
@@ -702,9 +693,6 @@
       </c>
       <c r="J5" t="n">
         <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1363.64</v>
       </c>
       <c r="O5" t="n">
         <v>83354.64</v>
@@ -860,9 +848,6 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>1500</v>
-      </c>
       <c r="O2" t="n">
         <v>66796</v>
       </c>
@@ -911,9 +896,6 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>1295.45</v>
-      </c>
       <c r="O3" t="n">
         <v>75743.28</v>
       </c>
@@ -962,9 +944,6 @@
       <c r="J4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
-        <v>1261.36</v>
-      </c>
       <c r="O4" t="n">
         <v>77032.92</v>
       </c>
@@ -1012,9 +991,6 @@
       </c>
       <c r="J5" t="n">
         <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1363.64</v>
       </c>
       <c r="O5" t="n">
         <v>83354.64</v>
@@ -1170,9 +1146,6 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>1500</v>
-      </c>
       <c r="O2" t="n">
         <v>66796</v>
       </c>
@@ -1221,9 +1194,6 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>1295.45</v>
-      </c>
       <c r="O3" t="n">
         <v>75743.28</v>
       </c>
@@ -1272,9 +1242,6 @@
       <c r="J4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
-        <v>1261.36</v>
-      </c>
       <c r="O4" t="n">
         <v>77032.92</v>
       </c>
@@ -1322,9 +1289,6 @@
       </c>
       <c r="J5" t="n">
         <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1363.64</v>
       </c>
       <c r="O5" t="n">
         <v>83354.64</v>
@@ -1480,9 +1444,6 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>1500</v>
-      </c>
       <c r="O2" t="n">
         <v>66796</v>
       </c>
@@ -1531,9 +1492,6 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>1295.45</v>
-      </c>
       <c r="O3" t="n">
         <v>75743.28</v>
       </c>
@@ -1582,9 +1540,6 @@
       <c r="J4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
-        <v>1261.36</v>
-      </c>
       <c r="O4" t="n">
         <v>77032.92</v>
       </c>
@@ -1632,9 +1587,6 @@
       </c>
       <c r="J5" t="n">
         <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1363.64</v>
       </c>
       <c r="O5" t="n">
         <v>83354.64</v>
@@ -1790,9 +1742,6 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>750</v>
-      </c>
       <c r="O2" t="n">
         <v>33398</v>
       </c>
@@ -1841,9 +1790,6 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>681.8200000000001</v>
-      </c>
       <c r="O3" t="n">
         <v>37737.3</v>
       </c>
@@ -1892,9 +1838,6 @@
       <c r="J4" t="n">
         <v>20</v>
       </c>
-      <c r="N4" t="n">
-        <v>511.36</v>
-      </c>
       <c r="O4" t="n">
         <v>38076.15</v>
       </c>
@@ -1942,9 +1885,6 @@
       </c>
       <c r="J5" t="n">
         <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>170.45</v>
       </c>
       <c r="O5" t="n">
         <v>9445.450000000001</v>
@@ -2100,9 +2040,6 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>1500</v>
-      </c>
       <c r="O2" t="n">
         <v>34148</v>
       </c>
@@ -2151,9 +2088,6 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>1227.27</v>
-      </c>
       <c r="O3" t="n">
         <v>38619.62</v>
       </c>
@@ -2202,9 +2136,6 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>1500</v>
-      </c>
       <c r="O4" t="n">
         <v>40057.29</v>
       </c>
@@ -2252,9 +2183,6 @@
       </c>
       <c r="J5" t="n">
         <v>8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1090.91</v>
       </c>
       <c r="O5" t="n">
         <v>41158.91</v>
@@ -2410,9 +2338,6 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>1500</v>
-      </c>
       <c r="O2" t="n">
         <v>34148</v>
       </c>
@@ -2461,9 +2386,6 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>1227.27</v>
-      </c>
       <c r="O3" t="n">
         <v>38619.62</v>
       </c>
@@ -2512,9 +2434,6 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>1500</v>
-      </c>
       <c r="O4" t="n">
         <v>40057.29</v>
       </c>
@@ -2562,9 +2481,6 @@
       </c>
       <c r="J5" t="n">
         <v>8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1090.91</v>
       </c>
       <c r="O5" t="n">
         <v>41158.91</v>
@@ -2720,9 +2636,6 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
         <v>44520</v>
       </c>
@@ -2771,9 +2684,6 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
       <c r="O3" t="n">
         <v>40424.16</v>
       </c>
@@ -2822,9 +2732,6 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
         <v>28041.66</v>
       </c>
@@ -2871,9 +2778,6 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
